--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260804.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260804.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>99,084,000</t>
+          <t>36,919,540</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>36,919,540</t>
+          <t>99,084,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>3,639,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>3,639,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
